--- a/data/annotations/part_c/part_c_surface_cover_annotations.xlsx
+++ b/data/annotations/part_c/part_c_surface_cover_annotations.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -6876,7 +6876,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7624,7 +7624,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -8882,7 +8882,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -8984,7 +8984,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -10412,7 +10412,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -10650,7 +10650,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -11568,7 +11568,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -12860,7 +12860,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -13268,7 +13268,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -13370,7 +13370,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -13812,7 +13812,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -14050,7 +14050,7 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -14288,7 +14288,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -14322,7 +14322,7 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -14390,7 +14390,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -14424,7 +14424,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
@@ -14458,7 +14458,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
@@ -14662,7 +14662,7 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -14730,7 +14730,7 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
@@ -14832,7 +14832,7 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -14866,7 +14866,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
@@ -14968,7 +14968,7 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -15070,7 +15070,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
@@ -15308,7 +15308,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -15444,7 +15444,7 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
@@ -15478,7 +15478,7 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -15580,7 +15580,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -15614,7 +15614,7 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -15750,7 +15750,7 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
@@ -15784,7 +15784,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
@@ -15818,7 +15818,7 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -16056,7 +16056,7 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
@@ -16158,7 +16158,7 @@
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -16260,7 +16260,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -16498,7 +16498,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -16600,7 +16600,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -16634,7 +16634,7 @@
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -16770,7 +16770,7 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -16906,7 +16906,7 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -17042,7 +17042,7 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -17076,7 +17076,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -17110,7 +17110,7 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -17348,7 +17348,7 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -17552,7 +17552,7 @@
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -17620,7 +17620,7 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -17722,7 +17722,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -17824,7 +17824,7 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -17926,7 +17926,7 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -18062,7 +18062,7 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -18164,7 +18164,7 @@
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -18334,7 +18334,7 @@
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -18402,7 +18402,7 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -18470,7 +18470,7 @@
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -18640,7 +18640,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -18708,7 +18708,7 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -18742,7 +18742,7 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -18776,7 +18776,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -18810,7 +18810,7 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -18878,7 +18878,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
@@ -18912,7 +18912,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -18946,7 +18946,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -19116,7 +19116,7 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -19150,7 +19150,7 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -19184,7 +19184,7 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -19218,7 +19218,7 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -19490,7 +19490,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -19694,7 +19694,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -19728,7 +19728,7 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
@@ -19762,7 +19762,7 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -19830,7 +19830,7 @@
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -19898,7 +19898,7 @@
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -19932,7 +19932,7 @@
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -19966,7 +19966,7 @@
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -20068,7 +20068,7 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -20204,7 +20204,7 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -20238,7 +20238,7 @@
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
@@ -20340,7 +20340,7 @@
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
@@ -20476,7 +20476,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
@@ -20544,7 +20544,7 @@
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -20578,7 +20578,7 @@
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
@@ -20646,7 +20646,7 @@
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
@@ -20748,7 +20748,7 @@
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -20782,7 +20782,7 @@
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -20850,7 +20850,7 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -20952,7 +20952,7 @@
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -20986,7 +20986,7 @@
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
@@ -21020,7 +21020,7 @@
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -21122,7 +21122,7 @@
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -21190,7 +21190,7 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -21292,7 +21292,7 @@
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -21394,7 +21394,7 @@
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -21462,7 +21462,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -21496,7 +21496,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -21564,7 +21564,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -21666,7 +21666,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -21836,7 +21836,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -21904,7 +21904,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -21938,7 +21938,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -22006,7 +22006,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -22040,7 +22040,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -22074,7 +22074,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -22108,7 +22108,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -22142,7 +22142,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -22210,7 +22210,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -22244,7 +22244,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -22312,7 +22312,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -22482,7 +22482,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -22516,7 +22516,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -22652,7 +22652,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -22822,7 +22822,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -22924,7 +22924,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -22958,7 +22958,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -22992,7 +22992,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -23128,7 +23128,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -23162,7 +23162,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -23196,7 +23196,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -23230,7 +23230,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -23298,7 +23298,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -23434,7 +23434,7 @@
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -23502,7 +23502,7 @@
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -23570,7 +23570,7 @@
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -23672,7 +23672,7 @@
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -23740,7 +23740,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -23808,7 +23808,7 @@
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -23842,7 +23842,7 @@
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -23910,7 +23910,7 @@
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -23944,7 +23944,7 @@
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -23978,7 +23978,7 @@
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -24046,7 +24046,7 @@
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -24080,7 +24080,7 @@
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -24114,7 +24114,7 @@
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -24148,7 +24148,7 @@
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -24182,7 +24182,7 @@
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -24250,7 +24250,7 @@
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -24284,7 +24284,7 @@
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -24318,7 +24318,7 @@
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -24352,7 +24352,7 @@
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -24386,7 +24386,7 @@
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -24420,7 +24420,7 @@
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -24454,7 +24454,7 @@
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -24556,7 +24556,7 @@
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -24658,7 +24658,7 @@
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -24692,7 +24692,7 @@
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -24726,7 +24726,7 @@
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -24862,7 +24862,7 @@
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -24930,7 +24930,7 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -24964,7 +24964,7 @@
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -25032,7 +25032,7 @@
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -25066,7 +25066,7 @@
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -25100,7 +25100,7 @@
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -25134,7 +25134,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -25168,7 +25168,7 @@
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -25202,7 +25202,7 @@
       </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -25236,7 +25236,7 @@
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -25338,7 +25338,7 @@
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -25372,7 +25372,7 @@
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -25508,7 +25508,7 @@
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -25542,7 +25542,7 @@
       </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -25576,7 +25576,7 @@
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -25610,7 +25610,7 @@
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -25644,7 +25644,7 @@
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -25678,7 +25678,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -25712,7 +25712,7 @@
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -25814,7 +25814,7 @@
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -25848,7 +25848,7 @@
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -25950,7 +25950,7 @@
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -26018,7 +26018,7 @@
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -26052,7 +26052,7 @@
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -26086,7 +26086,7 @@
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -26154,7 +26154,7 @@
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -26188,7 +26188,7 @@
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -26222,7 +26222,7 @@
       </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G759" t="inlineStr">
@@ -26256,7 +26256,7 @@
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G761" t="inlineStr">
@@ -26324,7 +26324,7 @@
       </c>
       <c r="F762" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G762" t="inlineStr">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G763" t="inlineStr">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -26426,7 +26426,7 @@
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G765" t="inlineStr">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="F768" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G768" t="inlineStr">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -26630,7 +26630,7 @@
       </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G771" t="inlineStr">
@@ -26664,7 +26664,7 @@
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G772" t="inlineStr">
@@ -26698,7 +26698,7 @@
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G773" t="inlineStr">
@@ -26732,7 +26732,7 @@
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G774" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -26800,7 +26800,7 @@
       </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G776" t="inlineStr">
@@ -26834,7 +26834,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
